--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -4443,7 +4443,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
+          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Владелец не назначен</t>
+          <t>Участие ДУП на этапе регистрации не определено</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
+          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Владелец не назначен</t>
+          <t>Участие ДУП на этапе регистрации не определено</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">

--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Точка передачи нигде не формализована — владелец не назначен</t>
+          <t>Фактически переводит объект из реализации в сопровождение, но точка передачи нигде не формализована</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>единообразно не закреплён — см. 3.1, 3.2, 3.3</t>
+          <t>Директор ДУП и оба зама — единого владельца нет, см. 3.1–3.3</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>единого владельца нет — оба зама C</t>
+          <t>Оба зама ДУП — единый владелец не назначен</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Инициирует и участвует в сборе данных; владелец не назначен</t>
+          <t>Инициирует открытие филиала и участвует в сборе данных по региону</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>СТ</t>
+          <t>СТ (техническая служба)</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>единообразно не закреплён — см. 3.1, 3.2, 3.3</t>
+          <t>Директор ДУП и оба зама — единого владельца нет, см. 3.1–3.3</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>единого владельца нет — оба зама C</t>
+          <t>Оба зама ДУП — единый владелец не назначен</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>СТ</t>
+          <t>СТ (техническая служба)</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Точка передачи нигде не формализована — владелец не назначен</t>
+          <t>Фактически переводит объект из реализации в сопровождение, но точка передачи нигде не формализована</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Инициирует и участвует в сборе данных; владелец не назначен</t>
+          <t>Инициирует открытие филиала и участвует в сборе данных по региону</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">

--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -17,11 +17,11 @@
     <sheet name="Матрица стыков с ЦО" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Карта ролей ДУП'!$A$1:$R$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Карта ролей ДУП'!$A$1:$R$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Карта ролей ДУП'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДУП — генеральный владелец'!$A$3:$R$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'ДУП — генеральный владелец'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ДУП — участник'!$A$3:$R$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ДУП — участник'!$A$3:$R$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'ДУП — участник'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Зоны без владельца'!$A$3:$R$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Зоны без владельца'!$3:$3</definedName>
@@ -903,7 +903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6418,8 +6418,180 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Б.9</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr"/>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Б. Чужие процессы</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>Обеспечение персоналом</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по реализации (внутри ДУП)</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>HR, Филиал</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Матрица стыков с ЦО: HR передаёт оформление штата филиала и приказов; процессы 1.3, 3.2, Б.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Б.10</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr"/>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>Б. Чужие процессы</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Обеспечение ИТ-инфраструктурой проекта</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по реализации (внутри ДУП)</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>Зерек, СТ</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Матрица стыков с ЦО: интерфейс не был отражён в дереве процессов до версии 3 — рекомендовано включить</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R61"/>
+  <autoFilter ref="A1:R63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -8286,7 +8458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11560,8 +11732,180 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Б.9</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr"/>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Б. Чужие процессы</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>Обеспечение персоналом</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по реализации (внутри ДУП)</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>HR, Филиал</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>Матрица стыков с ЦО: HR передаёт оформление штата филиала и приказов; процессы 1.3, 3.2, Б.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Б.10</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr"/>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>Б. Чужие процессы</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Обеспечение ИТ-инфраструктурой проекта</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по реализации (внутри ДУП)</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>Зерек, СТ</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Матрица стыков с ЦО: интерфейс не был отражён в дереве процессов до версии 3 — рекомендовано включить</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:R38"/>
+  <autoFilter ref="A3:R40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -12236,7 +12580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -12291,7 +12635,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12650,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12665,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
@@ -12332,11 +12676,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12721,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -12558,7 +12902,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>2</v>
@@ -12567,7 +12911,7 @@
         <v>3</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -12722,7 +13066,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>ДУП + ДРБ (разделено)</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -12730,7 +13074,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="D30" s="20" t="n"/>
@@ -12742,7 +13086,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ДУП + ОСУ (разделено)</t>
+          <t>ДУП + ДРБ (разделено)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -12750,7 +13094,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D31" s="20" t="n"/>
@@ -12762,7 +13106,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>СТ (техническая служба)</t>
+          <t>ДУП + ОСУ (разделено)</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -12770,7 +13114,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Б.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D32" s="20" t="n"/>
@@ -12779,8 +13123,49 @@
       <c r="G32" s="20" t="n"/>
       <c r="H32" s="21" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Зерек (ИТ-инфраструктура)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Б.10</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="21" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>СТ (техническая служба)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Б.7</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="21" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="C33:H33"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C24:H24"/>
@@ -12791,6 +13176,7 @@
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="C30:H30"/>
+    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Легенда" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Карта ролей ДУП" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ДУП — генеральный владелец" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ДУП — участник" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Зоны без владельца" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Сводка" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Выводы" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Матрица стыков с ЦО" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Легенда" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Карта ролей ДУП" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ДУП — генеральный владелец" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ДУП — участник" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Назначение владельцев" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Выводы" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матрица стыков с ЦО" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Карта ролей ДУП'!$A$1:$R$63</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Карта ролей ДУП'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДУП — генеральный владелец'!$A$3:$R$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ДУП — генеральный владелец'!$A$3:$R$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'ДУП — генеральный владелец'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ДУП — участник'!$A$3:$R$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ДУП — участник'!$A$3:$R$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'ДУП — участник'!$3:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Зоны без владельца'!$A$3:$R$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Зоны без владельца'!$3:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Назначение владельцев'!$A$4:$H$19</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Назначение владельцев'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Выводы'!$3:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Матрица стыков с ЦО'!$A$3:$G$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Матрица стыков с ЦО'!$3:$3</definedName>
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -666,7 +666,7 @@
         <is>
           <t>Подпроцесс в дереве ДУП и сквозной процесс — не одно и то же. Один и тот же подпроцесс может быть «своим» внутри ДУП и одновременно всего лишь этапом внутри процесса, которым целиком владеет другое подразделение.
 Пример. «Формирование реестра платежей и приоритизация» (1.9) — подпроцесс блока 1, внутри ДУП за него отвечает зам. по реализации. Но сквозным процессом оплаты владеет Финблок: ДУП агрегирует заявки филиалов и расставляет приоритеты, а решение об оплате и сам платёж — зона Финблока. В карте это видно по двум колонкам: «Генеральный бизнес-владелец — подразделение» = Финблок, «РОЛЬ ДУП» = Участник — исполнитель этапа (R).
-Так же устроены ФЭМ (1.5 — процесс Финблока), закупки (1.7 — процесс Закупщиков), прогноз поступлений (2.3 — процесс Финблока) и открытие филиала (3.2 — владельца нет вовсе).</t>
+Так же устроены ФЭМ (1.5 — процесс Финблока), закупки (1.7 — процесс Закупщиков), прогноз поступлений (2.3 — процесс Финблока) и открытие филиала: участок ДУП (3.2) и сквозной процесс (Б.5) — две разные записи с разными владельцами.</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Владелец не закреплён ни в должностных инструкциях, ни в кадровой матрице. Требует управленческого решения.</t>
+          <t>Владелец не закреплён ни в должностных инструкциях, ни в кадровой матрице. В этой версии карты таких записей нет: пятнадцать объектов, по которым владение отсутствовало или было размыто, закреплены за конкретными должностями.</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>3.2 / Б.5 Открытие нового филиала — первый и последний этап без владельца</t>
+          <t>Ноль записей. Решения и их основания — на листе «Назначение владельцев»</t>
         </is>
       </c>
     </row>
@@ -842,46 +842,58 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Лист «Сводка»</t>
+          <t>Лист «Назначение владельцев»</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Количественная картина: сколько процессов в каждой роли, по блокам и по подразделениям-владельцам.</t>
+          <t>Протокол закрепления владения: пятнадцать объектов, должность владельца, критерий Таблицы 5 Методики и документ, которым решение закрепляется.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Лист «Выводы»</t>
+          <t>Лист «Сводка»</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Управленческие следствия из карты в шести пунктах.</t>
+          <t>Количественная картина: сколько процессов в каждой роли, по блокам и по подразделениям-владельцам.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Лист «Матрица стыков с ЦО»</t>
+          <t>Лист «Выводы»</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>По каждому смежному подразделению: что ДУП получает, что отдаёт, где риск и что закрыть.</t>
+          <t>Управленческие следствия из карты в шести пунктах.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
+          <t>Лист «Матрица стыков с ЦО»</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>По каждому смежному подразделению: что ДУП получает, что отдаёт, где риск и что закрыть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
           <t>Колонка «Источник / статус подтверждения»</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Показывает, на чём основана запись. Формулировки «требует валидации» и «требует интервью» означают рабочую гипотезу, которую нужно подтвердить со смежным подразделением.</t>
         </is>
@@ -1140,7 +1152,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Зам. по строительству и реализации (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1160,7 +1172,7 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>Зам. по реализации</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -1190,7 +1202,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А; кадровая матрица — блоки 1 и 2 сегодня ведёт один человек</t>
+          <t>Дерево v4 разд. А. Владелец закреплён по критерию 1 Таблицы 5 Методики. До издания приказа о разделении замов обязанности исполняет зам. директора ДУП (п. 30–31 Методики: исполнение не приостанавливается)</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3348,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3386,7 +3398,7 @@
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А; сегодня совмещено с блоком 1</t>
+          <t>Дерево v4 разд. А. Владелец закреплён по критерию 1 Таблицы 5 Методики. До издания приказа о разделении замов фаза совмещена с блоком 1</t>
         </is>
       </c>
     </row>
@@ -3428,32 +3440,32 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Директор ДУП (целевое)</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
+          <t>Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>не закреплено</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Фактически переводит объект из реализации в сопровождение, но точка передачи нигде не формализована</t>
+          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -3463,7 +3475,7 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Пробел — критично при разделении замов</t>
+          <t>Не исполняется — чек-лист передачи не утверждён</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
@@ -3474,7 +3486,7 @@
       <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4: «момент/чек-лист передачи нигде не формализован»</t>
+          <t>Дерево v4: «момент/чек-лист передачи нигде не формализован». Владелец закреплён по критерию 1 Таблицы 5 Методики за передающей стороной: принимающая сторона не может отвечать за полноту того, что ей не передали</t>
         </is>
       </c>
     </row>
@@ -4239,37 +4251,37 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>не закреплён ни в одной ДИ</t>
-        </is>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>A? / R?</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Должен передавать сведения от эксплуатации владельцу ТЗ и закупок</t>
+          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>не закреплён</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>Менеджер проектов (предположительно)</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
@@ -4279,7 +4291,7 @@
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется регулярно</t>
+          <t>Не исполняется регулярно — маршрут не утверждён</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
@@ -4294,7 +4306,7 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>RACI 2.7: «ни в одной ДИ явно не описано — риск повторения проблемы хомутов»</t>
+          <t>RACI 2.7: «ни в одной ДИ явно не описано — риск повторения проблемы хомутов». Владелец закреплён по критерию 1 Таблицы 5 Методики: дефект обнаруживает эксплуатация, она же несёт потери от его повторения</t>
         </is>
       </c>
     </row>
@@ -4428,27 +4440,27 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Директор ДУП и оба зама — единого владельца нет, см. 3.1–3.3</t>
-        </is>
-      </c>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>Совладелец — ответственность разделена</t>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>A размыт</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
+          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Подпроцессы закреплены за директором (3.1), замом по операционной деятельности (3.2, 3.3)</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>Директор ДУП (только 3.1)</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr">
@@ -4463,7 +4475,7 @@
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>Размыто</t>
+          <t>Исполняется частично — регламенты подпроцессов не утверждены</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -4478,7 +4490,7 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4: «Владелец: не закреплён единообразно»</t>
+          <t>Дерево v4: «Владелец: не закреплён единообразно». Владелец закреплён по Таблице 4 Методики как за курирующим руководителем кросс-функционального процесса; п. 24 — полномочий заместителя для маршрута через HR, Юр блок и Финблок недостаточно</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4599,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Открытие нового филиала</t>
+          <t>Участие ДУП в открытии нового филиала</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -4607,37 +4619,37 @@
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Юр блок — условно, владелец со стороны ДУП не назван</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>не закреплено</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>В интервью куратор ведёт открытие сам, но ни в одной из 4 ДИ обязанность не встречается</t>
+          <t>Отвечает за участок ДУП в открытии филиала: обоснование потребности, данные по региону, приём работающей площадки и закрепление куратора</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>Куратор филиала (по факту)</t>
+          <t>Куратор филиала</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -4647,7 +4659,7 @@
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>«Ничья» зона</t>
+          <t>Не исполняется по регламенту — порядок открытия не утверждён</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -4658,7 +4670,7 @@
       <c r="Q41" s="6" t="inlineStr"/>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>RACI 3.2 и дерево v4 разд. Б: без владельца и первый, и последний этап</t>
+          <t>RACI 3.2 и дерево v4 разд. Б: ранее без владельца и первый, и последний этап. Владелец закреплён по критериям 1 и 3 Таблицы 5 Методики. Запись описывает только участок ДУП; сквозным процессом владеет директор ДУП (Б.5)</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4712,17 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Оба зама ДУП — единый владелец не назначен</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Совладелец — ответственность разделена</t>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>C / C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -4720,12 +4732,12 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>Оба зама</t>
+          <t>Менеджер проектов, куратор филиала</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
@@ -4735,7 +4747,7 @@
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>Размыто — разделено по фазе</t>
+          <t>Исполняется частично — порядок обращений не утверждён</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
@@ -4750,7 +4762,7 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>RACI 3.3: «формально разделено по фазе — единого владельца нет»</t>
+          <t>RACI 3.3: «формально разделено по фазе — единого владельца нет». Владелец закреплён по критерию 1 Таблицы 5 Методики: обращения филиалов касаются работающих объектов</t>
         </is>
       </c>
     </row>
@@ -4792,7 +4804,7 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Главный менеджер проектов (целевой); часть функционала — за Директором ДУП</t>
+          <t>Главный менеджер проектов</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -4827,7 +4839,7 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>Частично — роль новая</t>
+          <t>Исполняется частично — полномочия ПМО не закреплены приказом</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -4842,7 +4854,7 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору</t>
+          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору. Владелец закреплён по критерию 2 Таблицы 5 Методики. По п. 24 право останавливать проект по результатам аудита нужно закрепить приказом — иначе полномочий владельца недостаточно</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5233,7 @@
       <c r="D48" s="17" t="inlineStr"/>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -5309,7 +5321,7 @@
       <c r="D49" s="17" t="inlineStr"/>
       <c r="E49" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -5397,7 +5409,7 @@
       </c>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -5485,7 +5497,7 @@
       </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -5573,7 +5585,7 @@
       </c>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -5657,7 +5669,7 @@
       <c r="D53" s="17" t="inlineStr"/>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -5745,7 +5757,7 @@
       <c r="D54" s="17" t="inlineStr"/>
       <c r="E54" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -5833,7 +5845,7 @@
       <c r="D55" s="17" t="inlineStr"/>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
@@ -5843,37 +5855,37 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Юр блок — условно</t>
-        </is>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>Инициирует открытие филиала и участвует в сборе данных по региону</t>
+          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Директор ДУП</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
-          <t>Куратор филиала (по факту)</t>
+          <t>Куратор филиала</t>
         </is>
       </c>
       <c r="N55" s="6" t="inlineStr">
@@ -5883,7 +5895,7 @@
       </c>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>«Ничья» зона на первом и последнем этапе</t>
+          <t>Не исполняется по регламенту — сквозной маршрут не утверждён</t>
         </is>
       </c>
       <c r="P55" s="6" t="inlineStr">
@@ -5894,7 +5906,7 @@
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б: «владелец первого и последнего этапа не определён ни в ДИ, ни в кадровой матрице»</t>
+          <t>Дерево v4 разд. Б: «владелец первого и последнего этапа не определён ни в ДИ, ни в кадровой матрице». Владелец закреплён по критерию 1 Таблицы 5 и Таблице 4 Методики (кросс-функциональный процесс — курирующий руководитель). Назначение владельца чужого сквозного процесса ДУП в одностороннем порядке не утверждает: требуется процедура § 5 главы 5 Методики</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5933,7 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -5931,32 +5943,32 @@
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>ДУП</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>Инициирует открытие при отсутствии филиала в регионе</t>
+          <t>Обосновывает потребность в филиале и собирает данные по региону</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr">
@@ -5971,7 +5983,7 @@
       </c>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>«Ничья» зона</t>
+          <t>Не исполняется по регламенту — форма обоснования не утверждена</t>
         </is>
       </c>
       <c r="P56" s="6" t="inlineStr">
@@ -5982,7 +5994,7 @@
       <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б, этап 1</t>
+          <t>Дерево v4 разд. Б, этап 1. Владелец закреплён по Таблице 4 Методики: этап идёт в границах операционного контура ДУП</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6021,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr">
@@ -6097,7 +6109,7 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -6107,37 +6119,37 @@
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Участие ДУП на этапе регистрации не определено</t>
+          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Куратор филиала</t>
         </is>
       </c>
       <c r="N58" s="6" t="inlineStr">
@@ -6147,7 +6159,7 @@
       </c>
       <c r="O58" s="6" t="inlineStr">
         <is>
-          <t>«Ничья» зона</t>
+          <t>Исполняется — норматив срока регистрации не согласован</t>
         </is>
       </c>
       <c r="P58" s="6" t="inlineStr">
@@ -6158,7 +6170,7 @@
       <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б, этап 3</t>
+          <t>Дерево v4 разд. Б, этап 3. Владелец закреплён по Таблице 4 и п. 17 Методики: этап целиком выполняется Юр блоком. ДУП здесь клиент — вместо роли владельца нужен SLA</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6193,7 @@
       <c r="D59" s="17" t="inlineStr"/>
       <c r="E59" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
@@ -6269,7 +6281,7 @@
       <c r="D60" s="17" t="inlineStr"/>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -6353,7 +6365,7 @@
       <c r="D61" s="17" t="inlineStr"/>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -6437,7 +6449,7 @@
       <c r="D62" s="17" t="inlineStr"/>
       <c r="E62" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -6487,7 +6499,7 @@
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>Исполняется</t>
+          <t>Исполняется; норматив срока оформления не согласован</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
@@ -6502,7 +6514,7 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>Матрица стыков с ЦО: HR передаёт оформление штата филиала и приказов; процессы 1.3, 3.2, Б.5</t>
+          <t>Матрица стыков с ЦО: HR передаёт оформление штата филиала и приказов; процессы 1.3, 3.2, Б.5. Владелец подтверждён; ДУП здесь клиент — требуется SLA на срок оформления приказов</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6537,7 @@
       <c r="D63" s="17" t="inlineStr"/>
       <c r="E63" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -6603,7 +6615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6847,7 +6859,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Зам. по строительству и реализации (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -6867,7 +6879,7 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>Зам. по реализации</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -6897,7 +6909,7 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А; кадровая матрица — блоки 1 и 2 сегодня ведёт один человек</t>
+          <t>Дерево v4 разд. А. Владелец закреплён по критерию 1 Таблицы 5 Методики. До издания приказа о разделении замов обязанности исполняет зам. директора ДУП (п. 30–31 Методики: исполнение не приостанавливается)</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7495,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности (целевой) / Зам. директора ДУП — Власов Д.О. (факт)</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -7533,14 +7545,14 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А; сегодня совмещено с блоком 1</t>
+          <t>Дерево v4 разд. А. Владелец закреплён по критерию 1 Таблицы 5 Методики. До издания приказа о разделении замов фаза совмещена с блоком 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -7550,7 +7562,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Организация поверки оборудования</t>
+          <t>Передача проекта «реализация → сопровождение»</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
@@ -7565,7 +7577,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Поверка средств измерений</t>
+          <t>Передача проекта между блоками 1 и 2</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -7575,7 +7587,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -7590,12 +7602,12 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
+          <t>Готовит и передаёт комплект объекта в сопровождение; отвечает за полноту комплекта на дату передачи</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности</t>
+          <t>Зам. по строительству и реализации</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -7605,34 +7617,30 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Лаборатория (исполнитель), Филиал</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — методика устарела</t>
+          <t>Не исполняется — чек-лист передачи не утверждён</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>RACI 2.1: «↔ Лаборатория (исполняет)»; ~6 000 комплексов</t>
+          <t>Дерево v4: «момент/чек-лист передачи нигде не формализован». Владелец закреплён по критерию 1 Таблицы 5 Методики за передающей стороной: принимающая сторона не может отвечать за полноту того, что ей не передали</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
@@ -7642,7 +7650,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Сопровождение канала связи</t>
+          <t>Организация поверки оборудования</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
@@ -7657,7 +7665,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>Эксплуатация канала связи объекта</t>
+          <t>Поверка средств измерений</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -7667,64 +7675,64 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
+          <t>Зам. по операционной деятельности (исполнитель — внешняя лаборатория)</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Инициирует и оплачивает поверку; исполняет внешняя лаборатория</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
           <t>Зам. по операционной деятельности</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Генеральный владелец (A)</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Контролирует работоспособность канала связи объекта</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>Зам. по операционной деятельности</t>
-        </is>
-      </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>Менеджер проектов, филиал</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>СТ, Зерек, оператор связи</t>
+          <t>Лаборатория (исполнитель), Филиал</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>Исполняется</t>
+          <t>Не исполняется — методика устарела</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>RACI 2.2</t>
+          <t>RACI 2.1: «↔ Лаборатория (исполняет)»; ~6 000 комплексов</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -7734,7 +7742,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Обработка запросов на перенос оборудования</t>
+          <t>Сопровождение канала связи</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
@@ -7749,7 +7757,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Перенос оборудования по запросу госпартнёра</t>
+          <t>Эксплуатация канала связи объекта</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -7774,7 +7782,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
+          <t>Контролирует работоспособность канала связи объекта</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
@@ -7789,560 +7797,564 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>Госпартнёр (инициирует), СТ</t>
+          <t>СТ, Зерек, оператор связи</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — учёт «факт против ФЭМ» отсутствует</t>
+          <t>Исполняется</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>RACI 2.5</t>
+          <t>RACI 2.2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Обработка запросов на перенос оборудования</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>2. Сопровождение</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Перенос оборудования по запросу госпартнёра</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Обрабатывает запрос, согласует с филиалом, госпартнёром и оператором связи</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов, филиал</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>Госпартнёр (инициирует), СТ</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>Не исполняется — учёт «факт против ФЭМ» отсутствует</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>RACI 2.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>2. Сопровождение</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Извлечённые уроки по качеству компонентов</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Передаёт сведения о дефектах от эксплуатации владельцу ТЗ и закупок</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>СТ, Закупщики, Филиал</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>Не исполняется регулярно — маршрут не утверждён</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>RACI 2.7: «ни в одной ДИ явно не описано — риск повторения проблемы хомутов». Владелец закреплён по критерию 1 Таблицы 5 Методики: дефект обнаруживает эксплуатация, она же несёт потери от его повторения</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
           <t>2.8</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Отчётность руководству и госпартнёру (операционный статус)</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>2. Сопровождение</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>Отчётность по проектам</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>Зам. по операционной деятельности</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Генеральный владелец (A)</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>Готовит ежемесячную отчётность госпартнёру и регулярную — руководству</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>Зам. по операционной деятельности</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Менеджер проектов, младший МП</t>
         </is>
       </c>
-      <c r="N16" s="6" t="inlineStr">
+      <c r="N18" s="6" t="inlineStr">
         <is>
           <t>Госпартнёр, Акимат</t>
         </is>
       </c>
-      <c r="O16" s="6" t="inlineStr">
+      <c r="O18" s="6" t="inlineStr">
         <is>
           <t>Дублируется с 1.8 и 4.3</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>RACI 2.8 и находка о дублировании отчётности в трёх ДИ</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>ДУП.0</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>3. Филиальная сеть</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Подпроцессы закреплены за директором (3.1), замом по операционной деятельности (3.2, 3.3)</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Замы ДУП</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>HR, Юр блок, Филиалы</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется частично — регламенты подпроцессов не утверждены</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>Дерево v4: «Владелец: не закреплён единообразно». Владелец закреплён по Таблице 4 Методики как за курирующим руководителем кросс-функционального процесса; п. 24 — полномочий заместителя для маршрута через HR, Юр блок и Финблок недостаточно</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Назначение куратора на филиал / проект</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>3. Филиальная сеть</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>Управление филиальной сетью</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>Директор ДУП</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>Генеральный владелец (A)</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>Закрепляет ответственного менеджера ДУП за регионом</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>Директор ДУП</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>Директор ДУП</t>
         </is>
       </c>
-      <c r="N17" s="6" t="inlineStr">
+      <c r="N20" s="6" t="inlineStr">
         <is>
           <t>Филиал, HR</t>
         </is>
       </c>
-      <c r="O17" s="6" t="inlineStr">
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>Исполняется</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>RACI 3.1 (A — директор ДУП)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Методология и контроль качества (ПМО)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>ДУП.0</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>4. Методология/ПМО</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>Методология проектного управления и контроль качества</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Участие ДУП в открытии нового филиала</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>3. Филиальная сеть</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала (см. Б.5)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов (целевой); часть функционала — за Директором ДУП</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>Генеральный владелец (A)</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов, младший МП</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>Все блоки</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>Частично — роль новая</t>
-        </is>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>14, 15</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>4. Методология/ПМО</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>Методология проектного управления</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>Генеральный владелец (A)</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t>Младший менеджер проектов</t>
-        </is>
-      </c>
-      <c r="N19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>Устарело — Confluence 2021, архив 28%</t>
-        </is>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>RACI 4.1; кадровая матрица дублирует функцию за Директором ДУП</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Контроль качества и полноты проектных данных</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>4. Методология/ПМО</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Контроль качества проектных данных</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>Генеральный владелец (A)</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>Проверяет полноту и корректность информации по всем проектам обоих блоков</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>Младший менеджер проектов</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>Платформа портфеля</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr">
-        <is>
-          <t>Не исполняется — аудит остановлен после 2020</t>
-        </is>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr"/>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>RACI 4.2; чек-листы аудита методологии стр. 889–907</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>4.2.1</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Аудит проектной документации по чек-листам</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>4.2</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>4. Методология/ПМО</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Контроль качества проектных данных</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>ДУП</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>Главный менеджер проектов</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>Генеральный владелец (A)</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Проводит аудит по трём чек-листам методологии</t>
+          <t>Отвечает за участок ДУП в открытии филиала: обоснование потребности, данные по региону, приём работающей площадки и закрепление куратора</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>Главный менеджер проектов</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>Младший менеджер проектов</t>
+          <t>Куратор филиала</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Филиал</t>
+          <t>Юр блок, HR, Финблок</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется</t>
+          <t>Не исполняется по регламенту — порядок открытия не утверждён</t>
         </is>
       </c>
       <c r="P21" s="6" t="inlineStr">
@@ -8353,100 +8365,724 @@
       <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr">
         <is>
+          <t>RACI 3.2 и дерево v4 разд. Б: ранее без владельца и первый, и последний этап. Владелец закреплён по критериям 1 и 3 Таблицы 5 Методики. Запись описывает только участок ДУП; сквозным процессом владеет директор ДУП (Б.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>3. Филиальная сеть</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Менеджер проектов, куратор филиала</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>Филиал</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется частично — порядок обращений не утверждён</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>RACI 3.3: «формально разделено по фазе — единого владельца нет». Владелец закреплён по критерию 1 Таблицы 5 Методики: обращения филиалов касаются работающих объектов</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>ДУП.0</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>4. Методология/ПМО</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Методология проектного управления и контроль качества</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Сквозной для блоков 1 и 2: методология, качество данных, портфельная отчётность</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов, младший МП</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>Все блоки</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>Исполняется частично — полномочия ПМО не закреплены приказом</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>14, 15</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору. Владелец закреплён по критерию 2 Таблицы 5 Методики. По п. 24 право останавливать проект по результатам аудита нужно закрепить приказом — иначе полномочий владельца недостаточно</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Разработка и поддержка методологии, шаблонов, реестров</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>4. Методология/ПМО</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Методология проектного управления</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Разрабатывает и поддерживает единые инструменты проектного управления</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>Младший менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>Устарело — Confluence 2021, архив 28%</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>RACI 4.1; кадровая матрица дублирует функцию за Директором ДУП</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Контроль качества и полноты проектных данных</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>4. Методология/ПМО</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Контроль качества проектных данных</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Проверяет полноту и корректность информации по всем проектам обоих блоков</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>Младший менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>Платформа портфеля</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>Не исполняется — аудит остановлен после 2020</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>RACI 4.2; чек-листы аудита методологии стр. 889–907</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Аудит проектной документации по чек-листам</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>4. Методология/ПМО</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Контроль качества проектных данных</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Проводит аудит по трём чек-листам методологии</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>Младший менеджер проектов</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>Филиал</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>Не исполняется</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
           <t>Чек-листы методологии; пилот на одном филиале</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Портфельная отчётность руководству и заказчикам</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>4. Методология/ПМО</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>Отчётность по портфелю</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>Главный менеджер проектов</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>Генеральный владелец (A)</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J27" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K22" s="6" t="inlineStr">
+      <c r="K27" s="6" t="inlineStr">
         <is>
           <t>Готовит материалы для директора и Товарищества на уровне всего портфеля</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="L27" s="6" t="inlineStr">
         <is>
           <t>Главный менеджер проектов</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>Главный менеджер проектов</t>
         </is>
       </c>
-      <c r="N22" s="6" t="inlineStr">
+      <c r="N27" s="6" t="inlineStr">
         <is>
           <t>Правление</t>
         </is>
       </c>
-      <c r="O22" s="6" t="inlineStr">
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>Дублируется с 1.8 и 2.8</t>
         </is>
       </c>
-      <c r="P22" s="6" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>RACI 4.3: «пересекается с 1.8/2.8 — развести проектный и портфельный уровень»</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Б.5</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr"/>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Б. Сквозные процессы</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Отвечает за сквозной маршрут Юр → HR → Финблок → ДУП и за работающий филиал на выходе</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Куратор филиала</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>Юр блок, HR, Финблок</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>Не исполняется по регламенту — сквозной маршрут не утверждён</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>Дерево v4 разд. Б: «владелец первого и последнего этапа не определён ни в ДИ, ни в кадровой матрице». Владелец закреплён по критерию 1 Таблицы 5 и Таблице 4 Методики (кросс-функциональный процесс — курирующий руководитель). Назначение владельца чужого сквозного процесса ДУП в одностороннем порядке не утверждает: требуется процедура § 5 главы 5 Методики</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Б.5.1</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Инициирование, участие в сборе данных</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Б.5</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Б. Сквозные процессы</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Открытие нового филиала</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Генеральный владелец (A)</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Обосновывает потребность в филиале и собирает данные по региону</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>Куратор филиала</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>Не исполняется по регламенту — форма обоснования не утверждена</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>Дерево v4 разд. Б, этап 1. Владелец закреплён по Таблице 4 Методики: этап идёт в границах операционного контура ДУП</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:R22"/>
+  <autoFilter ref="A3:R29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -8458,7 +9094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R40"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10593,79 +11229,75 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Б.1</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Управление филиальной сетью</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>ДУП.0</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>3. Филиальная сеть</t>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Согласование бюджета проекта / ФЭМ</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr"/>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Управление филиальной сетью</t>
+          <t>Согласование бюджета проекта / ФЭМ</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>ДУП</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>Директор ДУП и оба зама — единого владельца нет, см. 3.1–3.3</t>
-        </is>
-      </c>
-      <c r="I26" s="7" t="inlineStr">
-        <is>
-          <t>Совладелец — ответственность разделена</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Участник — исполнитель этапа (R)</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>A размыт</t>
+          <t>R на первом этапе</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Ведёт филиальную сеть: кураторы, открытие филиалов, отношения вне проектов. Владение разнесено между директором (3.1), «никем» (3.2) и обоими замами (3.3)</t>
+          <t>Формирует ФЭМ (подпроцесс 1.5) — это только первый этап процесса</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>Директор ДУП (только 3.1)</t>
+          <t>Зам. по реализации (внутри ДУП)</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>Замы ДУП</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>HR, Юр блок, Филиалы</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>Размыто</t>
+          <t>Не исполняется — нормативы устарели</t>
         </is>
       </c>
       <c r="P26" s="6" t="inlineStr">
@@ -10675,89 +11307,85 @@
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4: «Владелец: не закреплён единообразно»</t>
+          <t>Дерево v4 разд. Б; требует интервью с Финблоком — возможно, часть ФЭМ делает сам Финблок</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>Подпроцесс</t>
-        </is>
-      </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>3. Филиальная сеть</t>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Б.2</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Финансовое закрытие проекта</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr"/>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Управление филиальной сетью</t>
+          <t>Финансовое закрытие проекта</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>ДУП</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Оба зама ДУП — единый владелец не назначен</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>Совладелец — ответственность разделена</t>
+          <t>Финблок</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>C / C</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Взаимодействие с директорами и главными инженерами вне рамок проекта</t>
+          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>не назначен</t>
+          <t>Зам. по операционной деятельности (внутри ДУП)</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>Оба зама</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>Филиал</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>Размыто — разделено по фазе</t>
+          <t>Не в дереве ДУП как ветка</t>
         </is>
       </c>
       <c r="P27" s="6" t="inlineStr">
@@ -10765,42 +11393,42 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="Q27" s="6" t="inlineStr"/>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>RACI 3.3: «формально разделено по фазе — единого владельца нет»</t>
+          <t>RACI Б.1 — единственный процесс раздела Б без отдельной строки RACI ранее</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>Б.1</t>
+          <t>Б.2.1</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Процесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>Согласование бюджета проекта / ФЭМ</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr"/>
+          <t>Служебная записка о необходимости закрытия</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Б.2</t>
+        </is>
+      </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>Согласование бюджета проекта / ФЭМ</t>
+          <t>Финансовое закрытие проекта</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -10820,17 +11448,17 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>R на первом этапе</t>
+          <t>R</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>Формирует ФЭМ (подпроцесс 1.5) — это только первый этап процесса</t>
+          <t>Инициирует закрытие служебной запиской</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>Зам. по реализации (внутри ДУП)</t>
+          <t>Зам. по операционной деятельности</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -10845,52 +11473,52 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — нормативы устарели</t>
+          <t>Частично</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr"/>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б; требует интервью с Финблоком — возможно, часть ФЭМ делает сам Финблок</t>
+          <t>Дерево v4 разд. Б, этап 1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
+          <t>Б.2.2</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
           <t>Б.2</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Б. Сквозные процессы</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>Финансовое закрытие проекта</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Б. Чужие процессы</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Финансовое закрытие проекта</t>
-        </is>
-      </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Финблок</t>
@@ -10901,57 +11529,57 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Участник — поставщик данных (C)</t>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Информируемый (I)</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Готовит служебную записку о необходимости закрытия — дальше процесс идёт в Финблоке</t>
+          <t>Предоставляет данные по запросу</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности (внутри ДУП)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>Менеджер проектов</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Финблок, Юр блок</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>Не в дереве ДУП как ветка</t>
+          <t>Вне периметра ДУП</t>
         </is>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr"/>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>RACI Б.1 — единственный процесс раздела Б без отдельной строки RACI ранее</t>
+          <t>Дерево v4 разд. Б, этап 2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>Б.2.1</t>
+          <t>Б.2.3</t>
         </is>
       </c>
       <c r="B30" s="17" t="inlineStr">
@@ -10961,7 +11589,7 @@
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>Служебная записка о необходимости закрытия</t>
+          <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
         </is>
       </c>
       <c r="D30" s="17" t="inlineStr">
@@ -10971,7 +11599,7 @@
       </c>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -10989,29 +11617,29 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>Участник — исполнитель этапа (R)</t>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Информируемый (I)</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Инициирует закрытие служебной запиской</t>
+          <t>Получает подтверждение закрытия проекта</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>Менеджер проектов</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
@@ -11021,50 +11649,46 @@
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>Частично</t>
+          <t>Вне периметра ДУП</t>
         </is>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr"/>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б, этап 1</t>
+          <t>Дерево v4 разд. Б, этап 3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>Б.2.2</t>
+          <t>Б.3</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Процесс</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Сбор актов сверок, уведомления о расторжении договоров</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Б.2</t>
-        </is>
-      </c>
+          <t>Прогноз поступлений и расходов</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr"/>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Финансовое закрытие проекта</t>
+          <t>Прогноз поступлений и расходов</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -11077,176 +11701,184 @@
           <t>Финблок</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>Информируемый (I)</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>Предоставляет данные по запросу</t>
+          <t>Поставляет данные и подтверждения по проектам (подпроцесс 2.3)</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Зам. по операционной деятельности (внутри ДУП)</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Менеджер проектов, филиал</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Финблок, Юр блок</t>
+          <t>Финблок</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>Вне периметра ДУП</t>
+          <t>Не исполняется — чат и ad-hoc</t>
         </is>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>6, 7</t>
+        </is>
+      </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б, этап 2</t>
+          <t>Дерево v4 разд. Б; интервью: «процесс финансистов» [00:08:48]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>Б.2.3</t>
+          <t>Б.4</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Процесс</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>Формирование бюджета на логистику / демонтаж, закрытие</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Б.2</t>
-        </is>
-      </c>
+          <t>Закупки выше упрощённого порога</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr"/>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>Финансовое закрытие проекта</t>
+          <t>Закупки выше упрощённого порога</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Закупщики (ОЛЖА)</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Информируемый (I)</t>
+          <t>Закупщики (ОЛЖА)</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Участник — исполнитель этапа (R)</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>R на входе + C на выходе</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Получает подтверждение закрытия проекта</t>
+          <t>Инициирует заявку и собирает спецификации; контролирует сроки и принимает поставку</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Зам. по реализации (внутри ДУП)</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Закупщики, СТ</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>Вне периметра ДУП</t>
+          <t>Не исполняется — нет нормативов сроков</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б, этап 3</t>
+          <t>Дерево v4 разд. Б — единственный процесс с участием ДУП и на входе, и на выходе</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>Б.3</t>
+          <t>Б.5.2</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Процесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Прогноз поступлений и расходов</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr"/>
+          <t>Подготовка пакета документов и доверенностей</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Б.5</t>
+        </is>
+      </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>Прогноз поступлений и расходов</t>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -11261,115 +11893,115 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Поставляет данные и подтверждения по проектам (подпроцесс 2.3)</t>
+          <t>Предоставляет данные по проекту и региону</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>Зам. по операционной деятельности (внутри ДУП)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>Менеджер проектов, филиал</t>
+          <t>Куратор филиала</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>Финблок</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — чат и ad-hoc</t>
+          <t>Исполняется</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>6, 7</t>
-        </is>
-      </c>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr"/>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б; интервью: «процесс финансистов» [00:08:48]</t>
+          <t>Дерево v4 разд. Б, этап 2; кадровая матрица</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t>Б.4</t>
+          <t>Б.5.3</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>Процесс</t>
+          <t>Этап</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>Закупки выше упрощённого порога</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr"/>
+          <t>Регистрация и запуск филиала</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Б.5</t>
+        </is>
+      </c>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Закупки выше упрощённого порога</t>
+          <t>Открытие нового филиала</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Закупщики (ОЛЖА)</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t>Участник — исполнитель этапа (R)</t>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>R на входе + C на выходе</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Инициирует заявку и собирает спецификации; контролирует сроки и принимает поставку</t>
+          <t>Передаёт данные для регистрации и принимает зарегистрированный филиал</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>Зам. по реализации (внутри ДУП)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>Менеджер проектов</t>
+          <t>Куратор филиала</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>Закупщики, СТ</t>
+          <t>Юр блок, HR, Финблок</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — нет нормативов сроков</t>
+          <t>Исполняется — норматив срока регистрации не согласован</t>
         </is>
       </c>
       <c r="P34" s="6" t="inlineStr">
@@ -11377,109 +12009,105 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="Q34" s="6" t="inlineStr"/>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б — единственный процесс с участием ДУП и на входе, и на выходе</t>
+          <t>Дерево v4 разд. Б, этап 3. Владелец закреплён по Таблице 4 и п. 17 Методики: этап целиком выполняется Юр блоком. ДУП здесь клиент — вместо роли владельца нужен SLA</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t>Б.5.2</t>
+          <t>Б.6</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Этап</t>
+          <t>Процесс</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Подготовка пакета документов и доверенностей</t>
-        </is>
-      </c>
-      <c r="D35" s="17" t="inlineStr">
-        <is>
-          <t>Б.5</t>
-        </is>
-      </c>
+          <t>Передача проекта от ДРБ в ДУП</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr"/>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>Открытие нового филиала</t>
+          <t>Presale, продажа и передача доходного проекта</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>ДРБ</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Участник — поставщик данных (C)</t>
+          <t>ДРБ</t>
+        </is>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>Участник — исполнитель этапа (R)</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>R на приёмке</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Предоставляет данные по проекту и региону</t>
+          <t>Принимает пакет и валидирует комплектность (подпроцесс 1.1)</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Зам. по реализации (внутри ДУП)</t>
         </is>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>Куратор филиала</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>ДРБ</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>Исполняется</t>
+          <t>Не исполняется — минимальный пакет не зафиксирован</t>
         </is>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>1, 4</t>
+        </is>
+      </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. Б, этап 2; кадровая матрица</t>
+          <t>Дерево v4, таблица внешних интерфейсов: «ДРБ владеет presale и продажей продукта»</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>Б.6</t>
+          <t>Б.7</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
@@ -11489,43 +12117,43 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>Передача проекта от ДРБ в ДУП</t>
+          <t>Производство, монтаж и калибровка оборудования</t>
         </is>
       </c>
       <c r="D36" s="17" t="inlineStr"/>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>Presale, продажа и передача доходного проекта</t>
+          <t>Производство и монтаж</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>ДРБ</t>
+          <t>СТ (техническая служба)</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>ДРБ</t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Участник — исполнитель этапа (R)</t>
+          <t>СТ (техническая служба)</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Участник — поставщик данных (C)</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>R на приёмке</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Принимает пакет и валидирует комплектность (подпроцесс 1.1)</t>
+          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -11540,34 +12168,30 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>ДРБ</t>
+          <t>СТ, Зерек, подрядчики</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — минимальный пакет не зафиксирован</t>
+          <t>Исполняется</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>1, 4</t>
-        </is>
-      </c>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr"/>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4, таблица внешних интерфейсов: «ДРБ владеет presale и продажей продукта»</t>
+          <t>Дерево v4, внешние интерфейсы: тех. карты, первичная калибровка и юстировка</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="inlineStr">
         <is>
-          <t>Б.7</t>
+          <t>Б.8</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
@@ -11577,28 +12201,28 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Производство, монтаж и калибровка оборудования</t>
+          <t>Юридическое сопровождение договоров с контрагентами</t>
         </is>
       </c>
       <c r="D37" s="17" t="inlineStr"/>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>Производство и монтаж</t>
+          <t>Подготовка и согласование договоров</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>СТ (техническая служба)</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>СТ (техническая служба)</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -11613,7 +12237,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>Даёт требования и принимает результат; тех. карты нужны до закупки</t>
+          <t>Предоставляет условия по проекту, согласовывает проект договора</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -11628,30 +12252,30 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>СТ, Зерек, подрядчики</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>Исполняется</t>
+          <t>Частично</t>
         </is>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr"/>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4, внешние интерфейсы: тех. карты, первичная калибровка и юстировка</t>
+          <t>Дерево v4, внешние интерфейсы; найден по кадровой матрице</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>Б.8</t>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
@@ -11661,28 +12285,28 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>Юридическое сопровождение договоров с контрагентами</t>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
         </is>
       </c>
       <c r="D38" s="17" t="inlineStr"/>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Подготовка и согласование договоров</t>
+          <t>Обеспечение персоналом</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="I38" s="9" t="inlineStr">
@@ -11697,7 +12321,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Предоставляет условия по проекту, согласовывает проект договора</t>
+          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -11712,12 +12336,12 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>HR, Филиал</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>Частично</t>
+          <t>Исполняется; норматив срока оформления не согласован</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
@@ -11725,17 +12349,21 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr"/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4, внешние интерфейсы; найден по кадровой матрице</t>
+          <t>Матрица стыков с ЦО: HR передаёт оформление штата филиала и приказов; процессы 1.3, 3.2, Б.5. Владелец подтверждён; ДУП здесь клиент — требуется SLA на срок оформления приказов</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>Б.9</t>
+          <t>Б.10</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
@@ -11745,28 +12373,28 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
         </is>
       </c>
       <c r="D39" s="17" t="inlineStr"/>
       <c r="E39" s="17" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
+          <t>Б. Сквозные процессы</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>Обеспечение персоналом</t>
+          <t>Обеспечение ИТ-инфраструктурой проекта</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Зерек (ИТ-инфраструктура)</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Зерек (ИТ-инфраструктура)</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
@@ -11781,7 +12409,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Формирует потребность в персонале и кураторах, принимает оформленный штат</t>
+          <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -11796,7 +12424,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>HR, Филиал</t>
+          <t>Зерек, СТ</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
@@ -11809,103 +12437,15 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="Q39" s="6" t="inlineStr"/>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>Матрица стыков с ЦО: HR передаёт оформление штата филиала и приказов; процессы 1.3, 3.2, Б.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Б.10</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>Процесс</t>
-        </is>
-      </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>Монтаж и запуск ИТ-инфраструктуры ЦОД</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="inlineStr"/>
-      <c r="E40" s="17" t="inlineStr">
-        <is>
-          <t>Б. Чужие процессы</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Обеспечение ИТ-инфраструктурой проекта</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Зерек (ИТ-инфраструктура)</t>
-        </is>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>Зерек (ИТ-инфраструктура)</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Участник — поставщик данных (C)</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>Передаёт техническую спецификацию и принимает смонтированную инфраструктуру</t>
-        </is>
-      </c>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>Зам. по реализации (внутри ДУП)</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>Менеджер проектов</t>
-        </is>
-      </c>
-      <c r="N40" s="6" t="inlineStr">
-        <is>
-          <t>Зерек, СТ</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="inlineStr">
-        <is>
-          <t>Исполняется</t>
-        </is>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
           <t>Матрица стыков с ЦО: интерфейс не был отражён в дереве процессов до версии 3 — рекомендовано включить</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R40"/>
+  <autoFilter ref="A3:R39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -11917,658 +12457,710 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Владелец не закреплён ни в должностных инструкциях, ни в кадровой матрице. Требуется управленческое решение — назначить владельца.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Закрепление владения: пятнадцать объектов, по которым владелец был не назначен или размыт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Владелец определяется по главе 4 Методики: пять критериев Таблицы 5 применяются строго последовательно, уровень должности берётся из Таблицы 4. Должность указана без ФИО — этого требует п. 16. Колонка «Чем закрепляется» показывает документ, без которого назначение остаётся намерением.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Код</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Объект владения</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Уровень</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Наименование процесса / подпроцесса / этапа</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Родитель</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Блок ДУП</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Сквозной процесс (end-to-end)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Генеральный бизнес-владелец — подразделение</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Генеральный бизнес-владелец — роль</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>РОЛЬ ДУП</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>RACI ДУП</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>Что делает ДУП</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Владелец со стороны ДУП (A)</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>Исполнитель ДУП (R)</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Внешние участники</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>Статус AS-IS</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>Узкое место №</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>Источник / статус подтверждения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Владелец — должность</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Подразделение</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Основание в Методике</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Почему именно эта должность</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Чем закрепляется</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Реализация проекта</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 1 Таблицы 5 — конечный результат</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Результат фазы — объект, введённый в эксплуатацию и принятый госпартнёром. Обязательства по срокам ввода несёт реализация, а не эксплуатация.</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Приказ о разделении заместителей и RACI v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Постпроектное сопровождение</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 1 Таблицы 5 — конечный результат</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Результат фазы — доходность объекта на всём сроке эксплуатации. Отвечать за неё может только та сторона, которая ведёт объект после ввода.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Приказ о разделении заместителей и RACI v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Передача проекта «реализация → сопровождение»</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>Передача проекта «реализация → сопровождение»</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>2. Сопровождение</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Передача проекта между блоками 1 и 2</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по строительству и реализации</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>ДУП</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Директор ДУП (целевое)</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>не закреплено</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Фактически переводит объект из реализации в сопровождение, но точка передачи нигде не формализована</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>Пробел — критично при разделении замов</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>Дерево v4: «момент/чек-лист передачи нигде не формализован»</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 1 Таблицы 5 — конечный результат</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Результат подпроцесса — принятый комплект объекта. За полноту комплекта отвечает передающая сторона: принимающая не может отвечать за то, чего ей не передали.</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Чек-лист передачи как приложение к регламенту блока 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2.7</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Обратная связь по дефектам компонентов → владелец ТЗ / закупки</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>2. Сопровождение</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Извлечённые уроки по качеству компонентов</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>не закреплён ни в одной ДИ</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>A? / R?</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Должен передавать сведения от эксплуатации владельцу ТЗ и закупок</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>не закреплён</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Менеджер проектов (предположительно)</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>СТ, Закупщики, Филиал</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>Не исполняется регулярно</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>RACI 2.7: «ни в одной ДИ явно не описано — риск повторения проблемы хомутов»</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 1 Таблицы 5 — конечный результат</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Результат — зафиксированный дефект компонента, дошедший до владельца ТЗ и закупок. Дефект обнаруживает эксплуатация, она же несёт потери от его повторения.</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Регламент обратной связи «эксплуатация → ТЗ → закупки»</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Управление филиальной сетью</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Таблица 4 — кросс-функциональный процесс; п. 24 — достаточность полномочий</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Процесс затрагивает HR, Юр блок и Финблок. Полномочий заместителя для сквозного маршрута недостаточно, владельцем назначается курирующий руководитель.</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Положение о ДУП, раздел «филиальная сеть»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Назначение куратора на филиал / проект</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение действующего владельца (RACI 3.1)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Назначение куратора — кадровое решение внутри департамента; право подписи есть только у директора ДУП.</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Запись уже закреплена, изменений не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Участие ДУП в открытии нового филиала</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>Подпроцесс</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Критерии 1 и 3 Таблицы 5 — результат и существенные риски</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Со стороны ДУП результат открытия филиала — работающая площадка с закреплённым куратором. Потери от задержки открытия несёт эксплуатация.</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>RACI v2 и регламент открытия филиала</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Общие отношения с филиалом (вне привязки к проекту)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 1 Таблицы 5 — конечный результат</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Отношения с филиалом вне проекта — это операционный контур: обращения филиалов касаются работающих объектов, а не строящихся.</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>RACI v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Методология и контроль качества (ПМО)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 2 Таблицы 5 — управленческие полномочия; п. 24 — закрепление полномочий</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Методологию и аудит качества данных ведёт ПМО. Полномочие останавливать проект по результатам аудита у роли отсутствует и должно быть закреплено отдельно.</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Приказ о полномочиях ПМО и положение о контроле качества данных</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Контроль качества и полноты проектных данных</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Подпроцесс</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение действующего владельца (RACI 4.2)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Контроль полноты проектных данных по обоим блокам ведёт та же роль, что разрабатывает методологию.</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Запись уже закреплена, изменений не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>4.2.1</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Аудит проектной документации по чек-листам</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Главный менеджер проектов</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение действующего владельца (Таблица 4 — уровень «этап»)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Аудит по чек-листам выполняется в границах ПМО, отдельного владельца не требует.</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Запись уже закреплена, изменений не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Б.5</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Открытие нового филиала</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>3. Филиальная сеть</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала (см. Б.5)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Юр блок — условно, владелец со стороны ДУП не назван</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>не закреплено</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>В интервью куратор ведёт открытие сам, но ни в одной из 4 ДИ обязанность не встречается</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>Куратор филиала (по факту)</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>Юр блок, HR, Финблок</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr">
-        <is>
-          <t>«Ничья» зона</t>
-        </is>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>RACI 3.2 и дерево v4 разд. Б: без владельца и первый, и последний этап</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Б.5</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Процесс</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>Б. Чужие процессы</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Юр блок — условно</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>Инициирует открытие филиала и участвует в сборе данных по региону</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>Куратор филиала (по факту)</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>Юр блок, HR, Финблок</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>«Ничья» зона на первом и последнем этапе</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Дерево v4 разд. Б: «владелец первого и последнего этапа не определён ни в ДИ, ни в кадровой матрице»</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Директор ДУП</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Критерий 1 Таблицы 5 и Таблица 4 — кросс-функциональный процесс</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Результат процесса — зарегистрированный и работающий филиал. Юр блок отвечает только за регистрацию, HR — только за штат; за работающий филиал целиком отвечает курирующий руководитель ДУП.</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Решение Операционного комитета по процедуре § 5 главы 5 Методики</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Б.5.1</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Инициирование, участие в сборе данных</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Инициирование, участие в сборе данных</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>Б.5</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>Б. Чужие процессы</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Инициирует открытие при отсутствии филиала в регионе</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Куратор филиала</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Зам. по операционной деятельности</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>ДУП</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Таблица 4 — уровень «этап»</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Этап выполняется в границах операционного контура ДУП: потребность в филиале выявляет тот, кто ведёт регион.</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Регламент открытия филиала, этап 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Б.5.3</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Регистрация и запуск филиала</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Этап</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Юр блок</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>«Ничья» зона</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Дерево v4 разд. Б, этап 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Б.5.3</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>Этап</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Регистрация и запуск филиала</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>Б.5</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>Б. Чужие процессы</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Открытие нового филиала</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>не определён</t>
-        </is>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>Не определён — «ничья» зона</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>Участие ДУП на этапе регистрации не определено</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>не назначен</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>Юр блок, HR, Финблок</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>«Ничья» зона</t>
-        </is>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>Дерево v4 разд. Б, этап 3</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Юр блок</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Таблица 4 — уровень «этап»; п. 17 — этап закрепляется за тем, в чьих границах идёт</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Регистрация филиала целиком выполняется Юр блоком. ДУП на этом этапе — клиент, поэтому вместо роли владельца нужен норматив срока.</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>SLA с Юр блоком: срок регистрации и состав пакета</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Б.9</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов по проекту и филиалу</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Процесс</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение действующего владельца (матрица стыков с ЦО)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Оформление штата и кадровых приказов — процесс HR. ДУП формирует потребность и принимает результат, поэтому нужен норматив срока оформления.</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>SLA с HR: срок оформления приказов по филиалу</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R9"/>
+  <autoFilter ref="A4:H19"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -12580,7 +13172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -12631,11 +13223,11 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>42%</t>
         </is>
       </c>
     </row>
@@ -12646,11 +13238,11 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
@@ -12676,11 +13268,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>21%</t>
         </is>
       </c>
     </row>
@@ -12706,11 +13298,11 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -12829,7 +13421,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>2</v>
@@ -12843,9 +13435,7 @@
       <c r="F17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="G17" s="6" t="inlineStr"/>
       <c r="H17" s="6" t="n">
         <v>12</v>
       </c>
@@ -12857,17 +13447,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="G18" s="6" t="inlineStr"/>
       <c r="H18" s="6" t="n">
         <v>4</v>
       </c>
@@ -12893,23 +13479,23 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Б. Чужие процессы</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr"/>
+          <t>Б. Сквозные процессы</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="C20" s="6" t="inlineStr"/>
       <c r="D20" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>3</v>
-      </c>
+      <c r="G20" s="6" t="inlineStr"/>
       <c r="H20" s="6" t="n">
         <v>16</v>
       </c>
@@ -12950,11 +13536,11 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>ДУП.0, 1, 1.1.2, 1.1.3, 1.2.2, 1.3, 1.4, 1.6, 1.8, 2, 2.0, 2.1, 2.2, 2.5, 2.8, 3, 3.1, 3.3, 4, 4.1, 4.2, 4.2.1, 4.3</t>
+          <t>ДУП.0, 1, 1.1.2, 1.1.3, 1.2.2, 1.3, 1.4, 1.6, 1.8, 2, 2.0, 2.1, 2.2, 2.5, 2.7, 2.8, 3, 3.1, 3.2, 3.3, 4, 4.1, 4.2, 4.2.1, 4.3, Б.5, Б.5.1</t>
         </is>
       </c>
       <c r="D24" s="20" t="n"/>
@@ -13026,15 +13612,15 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>не определён</t>
+          <t>Юр блок</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>2.7, 3.2, Б.5, Б.5.1, Б.5.3</t>
+          <t>Б.5.2, Б.5.3, Б.8</t>
         </is>
       </c>
       <c r="D28" s="20" t="n"/>
@@ -13046,15 +13632,15 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Юр блок</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Б.5.2, Б.8</t>
+          <t>Б.9</t>
         </is>
       </c>
       <c r="D29" s="20" t="n"/>
@@ -13066,7 +13652,7 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>ДУП + ДРБ (разделено)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -13074,7 +13660,7 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Б.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="D30" s="20" t="n"/>
@@ -13086,7 +13672,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>ДУП + ДРБ (разделено)</t>
+          <t>ДУП + ОСУ (разделено)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -13094,7 +13680,7 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="D31" s="20" t="n"/>
@@ -13106,7 +13692,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>ДУП + ОСУ (разделено)</t>
+          <t>Зерек (ИТ-инфраструктура)</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -13114,7 +13700,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>Б.10</t>
         </is>
       </c>
       <c r="D32" s="20" t="n"/>
@@ -13126,7 +13712,7 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>Зерек (ИТ-инфраструктура)</t>
+          <t>СТ (техническая служба)</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
@@ -13134,7 +13720,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Б.10</t>
+          <t>Б.7</t>
         </is>
       </c>
       <c r="D33" s="20" t="n"/>
@@ -13143,28 +13729,8 @@
       <c r="G33" s="20" t="n"/>
       <c r="H33" s="21" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>СТ (техническая служба)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Б.7</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="n"/>
-      <c r="E34" s="20" t="n"/>
-      <c r="F34" s="20" t="n"/>
-      <c r="G34" s="20" t="n"/>
-      <c r="H34" s="21" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="11">
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="C32:H32"/>
@@ -13176,7 +13742,6 @@
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="C29:H29"/>
     <mergeCell ref="C30:H30"/>
-    <mergeCell ref="C34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -13189,7 +13754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13266,22 +13831,46 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Зоны без владельца</t>
+          <t>Зон без владельца не осталось</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Открытие филиала (3.2 / Б.5), передача «реализация → сопровождение» (2.0) и обратная связь по дефектам (2.7) не закреплены ни в одной должностной инструкции.</t>
+          <t>Шесть объектов, которые не были закреплены ни в одной должностной инструкции — открытие филиала (3.2, Б.5, Б.5.1, Б.5.3), передача «реализация → сопровождение» (2.0) и обратная связь по дефектам (2.7), — получили владельца по критериям Таблицы 5 Методики. Ещё по девяти объектам владение уточнено или подтверждено. Основания по каждому — на листе «Назначение владельцев».</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Назначение — ещё не исполнение</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Шесть из пятнадцати решений держатся на документах, которых пока нет: приказ о разделении заместителей (объекты 1, 2, 2.0), приказ о полномочиях ПМО (4), решение Операционного комитета по сквозному маршруту открытия филиала (Б.5). До издания этих документов исполнение не приостанавливается (п. 30–31 Методики), но спрашивать за результат можно только с той должности, которая уже существует.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Пять объектов с разделённой ответственностью</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>1.1 (пакет от ДРБ), 1.2 (готовность продукта), 1.2.2 (gate), 2.4 (продление контракта) и 2.6 (вынесение на ОСУ) остаются со статусом «ответственность разделена». Это не «ничья» зона: ответственный назван с каждой стороны. Закрывается такое состояние не приказом внутри ДУП, а письменной точкой передачи и SLA со смежником.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
           <t>Что это значит для управления</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Там, где ДУП генеральный владелец, работает приказ и регламент. Там, где ДУП участник, нужен согласованный со смежным подразделением SLA на стык: состав данных, срок и ответственный с обеих сторон.</t>
         </is>
@@ -13484,17 +14073,17 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>3.2, Б.5, Б.8</t>
+          <t>3.2, Б.5, Б.5.3, Б.8</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Открытие филиала — «ничья» зона: владелец не назначен ни со стороны ДУП, ни в целом по процессу</t>
+          <t>Владелец открытия филиала закреплён за директором ДУП, но сквозной маршрут и срок регистрации со стороны Юр блока не согласованы</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Назначить владельца процесса и утвердить сквозной маршрут Юр → HR → Финблок → ДУП → филиал</t>
+          <t>Утвердить маршрут Юр → HR → Финблок → ДУП → филиал через Операционный комитет и подписать SLA на срок регистрации</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr"/>
@@ -13522,12 +14111,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Обратная связь по дефектам не закреплена ни в одной ДИ — риск повторения кейса «хомутов»</t>
+          <t>Владелец обратной связи по дефектам закреплён (2.7), но маршрут до владельца ТЗ и закупок не утверждён — риск повторения кейса «хомутов» сохраняется</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Назначить владельца процесса 2.7 и маршрут «эксплуатация → владелец ТЗ → закупки»</t>
+          <t>Утвердить регламент маршрута «эксплуатация → владелец ТЗ → закупки» и форму фиксации дефекта</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -13694,17 +14283,17 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>1.3, 3.2, Б.5</t>
+          <t>1.3, 3.2, Б.5, Б.9</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Разделение блоков 1 и 2 не внедрено — штатка остаётся предложением</t>
+          <t>Разделение блоков 1 и 2 не внедрено — штатка остаётся предложением; срок оформления кадровых приказов по филиалу не нормирован</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Приказ о разделении заместителей после утверждения чек-листа передачи</t>
+          <t>Приказ о разделении заместителей после утверждения чек-листа передачи; SLA с HR на срок оформления приказов</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">

--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -6499,7 +6499,7 @@
       </c>
       <c r="O62" s="6" t="inlineStr">
         <is>
-          <t>Исполняется; норматив срока оформления не согласован</t>
+          <t>Исполняется — норматив срока оформления не согласован</t>
         </is>
       </c>
       <c r="P62" s="6" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>Исполняется; норматив срока оформления не согласован</t>
+          <t>Исполняется — норматив срока оформления не согласован</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Шесть из пятнадцати решений держатся на документах, которых пока нет: приказ о разделении заместителей (объекты 1, 2, 2.0), приказ о полномочиях ПМО (4), решение Операционного комитета по сквозному маршруту открытия филиала (Б.5). До издания этих документов исполнение не приостанавливается (п. 30–31 Методики), но спрашивать за результат можно только с той должности, которая уже существует.</t>
+          <t>Пять из пятнадцати решений остаются намерением, пока нет документа. Приказ о разделении заместителей вводит сами должности владельцев блоков 1 и 2; приказ о полномочиях ПМО даёт владельцу методологии (4) право останавливать проект по результатам аудита; решение Операционного комитета утверждает сквозной маршрут открытия филиала (Б.5). Приказ о разделении, в свою очередь, выпускается после чек-листа передачи (2.0) — иначе объекты зависают между блоками. До издания этих документов исполнение не приостанавливается (п. 30–31 Методики), но спрашивать за результат можно только с той должности, которая уже существует.</t>
         </is>
       </c>
     </row>

--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -847,7 +847,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Протокол закрепления владения: пятнадцать объектов, должность владельца, критерий Таблицы 5 Методики и документ, которым решение закрепляется.</t>
+          <t>Протокол закрепления владения: 15 объектов, должность владельца, критерий Таблицы 5 Методики и документ, в котором решение зафиксировано.</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>Исполняется частично — полномочия ПМО не закреплены приказом</t>
+          <t>Исполняется частично — паспорт процесса не утверждён</t>
         </is>
       </c>
       <c r="P43" s="6" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору. Владелец закреплён по критерию 2 Таблицы 5 Методики. По п. 24 право останавливать проект по результатам аудита нужно закрепить приказом — иначе полномочий владельца недостаточно</t>
+          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору. Владелец закреплён по критерию 2 Таблицы 5 Методики, право останавливать проект по результатам аудита закреплено за той же ролью. Паспорт процесса и положение о контроле качества ещё не утверждены</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>Исполняется частично — полномочия ПМО не закреплены приказом</t>
+          <t>Исполняется частично — паспорт процесса не утверждён</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору. Владелец закреплён по критерию 2 Таблицы 5 Методики. По п. 24 право останавливать проект по результатам аудита нужно закрепить приказом — иначе полномочий владельца недостаточно</t>
+          <t>Дерево v4 разд. А, блок 4; репортит напрямую директору. Владелец закреплён по критерию 2 Таблицы 5 Методики, право останавливать проект по результатам аудита закреплено за той же ролью. Паспорт процесса и положение о контроле качества ещё не утверждены</t>
         </is>
       </c>
     </row>
@@ -12473,14 +12473,14 @@
     <row r="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Закрепление владения: пятнадцать объектов, по которым владелец был не назначен или размыт</t>
+          <t>Закрепление владения: 15 объектов, по которым владелец был не назначен или размыт</t>
         </is>
       </c>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Владелец определяется по главе 4 Методики: пять критериев Таблицы 5 применяются строго последовательно, уровень должности берётся из Таблицы 4. Должность указана без ФИО — этого требует п. 16. Колонка «Чем закрепляется» показывает документ, без которого назначение остаётся намерением.</t>
+          <t>Владелец определяется по главе 4 Методики: пять критериев Таблицы 5 применяются строго последовательно, уровень должности берётся из Таблицы 4. Должность указана без ФИО — этого требует п. 16. Все решения приняты и действуют; колонка «Где зафиксировано» показывает документ, в котором решение живёт дальше.</t>
         </is>
       </c>
     </row>
@@ -12522,7 +12522,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Чем закрепляется</t>
+          <t>Где зафиксировано</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Приказ о разделении заместителей и RACI v2</t>
+          <t>RACI v2 и паспорт процесса блока 1</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Приказ о разделении заместителей и RACI v2</t>
+          <t>RACI v2 и паспорт процесса блока 2</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Чек-лист передачи как приложение к регламенту блока 1</t>
+          <t>Чек-лист передачи как приложение к паспорту процесса блока 1</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Запись уже закреплена, изменений не требуется</t>
+          <t>Действующая запись RACI, изменений не требуется</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Методологию и аудит качества данных ведёт ПМО. Полномочие останавливать проект по результатам аудита у роли отсутствует и должно быть закреплено отдельно.</t>
+          <t>Методологию и аудит качества данных ведёт ПМО. Право останавливать проект по результатам аудита закреплено за той же ролью: иначе аудит не имеет последствий.</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Приказ о полномочиях ПМО и положение о контроле качества данных</t>
+          <t>Положение о контроле качества проектных данных</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12942,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Запись уже закреплена, изменений не требуется</t>
+          <t>Действующая запись RACI, изменений не требуется</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Запись уже закреплена, изменений не требуется</t>
+          <t>Действующая запись RACI, изменений не требуется</t>
         </is>
       </c>
     </row>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Решение Операционного комитета по процедуре § 5 главы 5 Методики</t>
+          <t>Регламент открытия филиала: сквозной маршрут за директором ДУП</t>
         </is>
       </c>
     </row>
@@ -13843,12 +13843,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Назначение — ещё не исполнение</t>
+          <t>Стоп-факторов для старта нет</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Пять из пятнадцати решений остаются намерением, пока нет документа. Приказ о разделении заместителей вводит сами должности владельцев блоков 1 и 2; приказ о полномочиях ПМО даёт владельцу методологии (4) право останавливать проект по результатам аудита; решение Операционного комитета утверждает сквозной маршрут открытия филиала (Б.5). Приказ о разделении, в свою очередь, выпускается после чек-листа передачи (2.0) — иначе объекты зависают между блоками. До издания этих документов исполнение не приостанавливается (п. 30–31 Методики), но спрашивать за результат можно только с той должности, которая уже существует.</t>
+          <t>Все 15 решений о владении приняты и действуют: у каждого объекта есть должность, с которой можно спрашивать за результат (п. 33 Методики). Документа, без которого нельзя начинать, не осталось — владение зафиксировано в RACI v2, Положении о ДУП и регламентах, перечисленных на листе «Назначение владельцев». Поэтому реинжиниринг начинается не с оформления полномочий, а с паспортов процессов и базовой линии: пока границы, вход, выход и показатели процесса не описаны (глава 8 и Приложение №2 Методики), улучшения не с чем сверять.</t>
         </is>
       </c>
     </row>

--- a/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
+++ b/dup_project/01_Процессы/ДУП_карта_ролей_в_процессах.xlsx
@@ -1547,7 +1547,7 @@
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>Пробел — процедуры нет</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P7" s="6" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — нормативы устарели</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P12" s="6" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — нет нормативов сроков</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P18" s="6" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — 3 потока не формализованы</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P23" s="6" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — ведётся в чате и ad-hoc</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P32" s="6" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O36" s="6" t="inlineStr">
         <is>
-          <t>Исполняется</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P36" s="6" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>Пробел — процедуры нет</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — нормативы устарели</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P9" s="6" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — нет нормативов сроков</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P14" s="6" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — 3 потока не формализованы</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P19" s="6" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>Не исполняется — ведётся в чате и ad-hoc</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P24" s="6" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>Исполняется</t>
+          <t>Складывается из подпроцессов</t>
         </is>
       </c>
       <c r="P28" s="6" t="inlineStr">
